--- a/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/03_MMFM3 - Hat Besleme ve İç Akış/EKG-LOJ-PLN-02_her_parca_ve_malzeme_icin_plan__pfep.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/12_Üretim ve Malzeme Akış Yönetimi/03_MMFM3 - Hat Besleme ve İç Akış/EKG-LOJ-PLN-02_her_parca_ve_malzeme_icin_plan__pfep.xlsx
@@ -846,7 +846,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Her Parça ve Malzeme İçin Plan - PFEP</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: PFEP stok ve ambalaj bilgileri sadeleştirildi; depolama ve ikmal şartları ayrı sekmeye alındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1014,7 +1015,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PLN-02&amp;C&amp;"Arial,Regular"&amp;11Her Parça ve Malzeme İçin Plan - PFEP</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 04.09.2026
+Revizyon nedeni: PFEP stok ve ambalaj bilgileri sadeleştirildi; depolama ve ikmal şartları ayrı sekmeye alındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>